--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484840_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484840_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4622</v>
+        <v>8.1417</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8799</v>
+        <v>7.7182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5823</v>
+        <v>0.4235</v>
       </c>
       <c r="G2" t="n">
         <v>7.0094</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.415</v>
+        <v>0.2645</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0582</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6432</v>
+        <v>0.4845</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0169</v>
+        <v>3.0955</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6642</v>
+        <v>1.6898</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3528</v>
+        <v>1.4057</v>
       </c>
       <c r="G3" t="n">
         <v>1.1739</v>
@@ -688,13 +688,13 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7488</v>
+        <v>0.8274</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7164</v>
+        <v>0.7421</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0324</v>
+        <v>0.0853</v>
       </c>
       <c r="V3" t="n">
         <v>-0.038</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1639</v>
+        <v>2.9072</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5755</v>
+        <v>0.0091</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7393</v>
+        <v>2.8981</v>
       </c>
       <c r="G4" t="n">
         <v>1.09</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2469</v>
+        <v>0.4964</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4086</v>
+        <v>0.176</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1617</v>
+        <v>0.3204</v>
       </c>
       <c r="V4" t="n">
         <v>0.9434</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>D. CLOSSET MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5773</v>
+        <v>0.4352</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0214</v>
+        <v>-0.9049</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4441</v>
+        <v>1.3402</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9404</v>
+        <v>-0.3404</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3367</v>
+        <v>-2.1201</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3963</v>
+        <v>1.7796</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5834</v>
+        <v>-1.1027</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1158</v>
+        <v>-1.843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6992</v>
+        <v>0.7403</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5238</v>
+        <v>0.7623</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2208</v>
+        <v>-0.277</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.303</v>
+        <v>1.0393</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8576</v>
+        <v>0.3983</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4196</v>
+        <v>0.1978</v>
       </c>
       <c r="U5" t="n">
-        <v>0.438</v>
+        <v>0.2005</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CLOSSET MARTINEZ</t>
+          <t>S. DAMULEVICIUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3726</v>
+        <v>0.0362</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0998</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4724</v>
+        <v>0.0362</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3404</v>
+        <v>-0.0814</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1201</v>
+        <v>-0.2113</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7796</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1027</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.843</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7403</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7623</v>
+        <v>-0.0814</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.277</v>
+        <v>-0.2113</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0393</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3357</v>
+        <v>0.1176</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3328</v>
+        <v>0.1176</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. DAMULEVICIUS</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.142</v>
+        <v>0.0227</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.611</v>
       </c>
       <c r="F7" t="n">
-        <v>0.142</v>
+        <v>0.6338</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0814</v>
+        <v>0.489</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2113</v>
+        <v>0.3506</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1299</v>
+        <v>0.1384</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.0508</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0423</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0814</v>
+        <v>0.4383</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2113</v>
+        <v>0.3083</v>
       </c>
       <c r="O7" t="n">
         <v>0.1299</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2234</v>
+        <v>0.2885</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0201</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2234</v>
+        <v>0.3086</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>R. MARTINEZ BERTOMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0482</v>
+        <v>-0.4027</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7085</v>
+        <v>-0.155</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6602</v>
+        <v>-0.2476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.489</v>
+        <v>1.2095</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3506</v>
+        <v>-0.529</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1384</v>
+        <v>1.7385</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0508</v>
+        <v>0.4143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0423</v>
+        <v>-0.2849</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4383</v>
+        <v>0.7951</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3083</v>
+        <v>-0.2442</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1299</v>
+        <v>1.0393</v>
       </c>
       <c r="P8" t="n">
         <v>-0.7548</v>
@@ -1078,28 +1078,28 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2175</v>
+        <v>0.3689</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1176</v>
+        <v>0.3741</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3351</v>
+        <v>-0.0053</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3018</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MARTINEZ BERTOMEU</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5182</v>
+        <v>-0.4705</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3499</v>
+        <v>0.1058</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1683</v>
+        <v>-0.5763</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2095</v>
+        <v>-0.9404</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.529</v>
+        <v>-1.3367</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7385</v>
+        <v>0.3963</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4143</v>
+        <v>0.5834</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2849</v>
+        <v>-0.1158</v>
       </c>
       <c r="L9" t="n">
         <v>0.6992</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7951</v>
+        <v>-1.5238</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2442</v>
+        <v>-1.2208</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0393</v>
+        <v>-0.303</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7548</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2534</v>
+        <v>0.8098</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1793</v>
+        <v>0.504</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0741</v>
+        <v>0.3057</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2262</v>
+        <v>0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.9054</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.177</v>
+        <v>-0.9905</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6557</v>
+        <v>-2.3634</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4788</v>
+        <v>1.373</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0897</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1769</v>
+        <v>0.3634</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2323</v>
+        <v>0.0601</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4092</v>
+        <v>0.3034</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6415999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3451</v>
+        <v>-1.0315</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0472</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3923</v>
+        <v>-0.9426</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1506</v>
@@ -1312,13 +1312,13 @@
         <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0623</v>
+        <v>0.2513</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3585</v>
+        <v>0.2224</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4209</v>
+        <v>0.0289</v>
       </c>
       <c r="V11" t="n">
         <v>1.2452</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2701</v>
+        <v>-2.2271</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4351</v>
+        <v>-0.1886</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8351</v>
+        <v>-2.0385</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6058</v>
+        <v>-2.6339</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7618</v>
+        <v>-0.5728</v>
       </c>
       <c r="I12" t="n">
-        <v>0.156</v>
+        <v>-2.061</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0117</v>
+        <v>-0.0492</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7286</v>
+        <v>1.1676</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7403</v>
+        <v>-1.2169</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6175</v>
+        <v>-2.5846</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0332</v>
+        <v>-1.7405</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5843</v>
+        <v>-0.8442</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8077</v>
+        <v>-0.348</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5349</v>
+        <v>-0.1394</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2728</v>
+        <v>-0.2087</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9401</v>
+        <v>-2.7863</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6371</v>
+        <v>-0.766</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.303</v>
+        <v>-2.0203</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6339</v>
+        <v>-2.6058</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5728</v>
+        <v>-2.7618</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.061</v>
+        <v>0.156</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0492</v>
+        <v>0.0117</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1676</v>
+        <v>-0.7286</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2169</v>
+        <v>0.7403</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5846</v>
+        <v>-2.6175</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7405</v>
+        <v>-2.0332</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8442</v>
+        <v>-0.5843</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7548</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0611</v>
+        <v>0.2916</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5879</v>
+        <v>0.2039</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4732</v>
+        <v>0.0876</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="14">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.436199999999999</v>
+        <v>6.729899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1511</v>
+        <v>4.445100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.285</v>
+        <v>2.2852</v>
       </c>
       <c r="G14" t="n">
         <v>1.1296</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0913</v>
+        <v>-3.091299999999999</v>
       </c>
       <c r="I14" t="n">
         <v>4.220800000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>8.214499999999997</v>
+        <v>8.214499999999999</v>
       </c>
       <c r="K14" t="n">
         <v>7.5677</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6466000000000001</v>
+        <v>0.6465999999999996</v>
       </c>
       <c r="M14" t="n">
         <v>-7.0847</v>
@@ -1546,13 +1546,13 @@
         <v>9.434999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8357</v>
+        <v>4.1297</v>
       </c>
       <c r="T14" t="n">
-        <v>1.807</v>
+        <v>2.101</v>
       </c>
       <c r="U14" t="n">
-        <v>2.028600000000001</v>
+        <v>2.0285</v>
       </c>
       <c r="V14" t="n">
         <v>3.3578</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3287</v>
+        <v>1.4424</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4018</v>
+        <v>-0.1846</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0731</v>
+        <v>1.627</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0804</v>
+        <v>2.2362</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.713</v>
+        <v>1.7186</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6325</v>
+        <v>0.5177</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6865</v>
+        <v>2.8496</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9461000000000001</v>
+        <v>2.2241</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7403</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7669</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6591</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-0.1078</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1322</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R15" t="n">
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>1.258</v>
+        <v>-1.0014</v>
       </c>
       <c r="T15" t="n">
-        <v>1.376</v>
+        <v>-0.8263</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1181</v>
+        <v>-0.1751</v>
       </c>
       <c r="V15" t="n">
-        <v>0.019</v>
+        <v>0.9624</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2828</v>
+        <v>0.6226</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2639</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3605</v>
+        <v>0.7266</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7692</v>
+        <v>1.0378</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1297</v>
+        <v>-0.3112</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2362</v>
+        <v>-0.0804</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7186</v>
+        <v>-0.713</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5177</v>
+        <v>0.6325</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8496</v>
+        <v>1.6865</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2241</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7403</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-1.7669</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-1.6591</v>
       </c>
       <c r="O16" t="n">
         <v>-0.1078</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0833</v>
+        <v>-0.3442</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4109</v>
+        <v>0.012</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3276</v>
+        <v>-0.3562</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9624</v>
+        <v>0.019</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6226</v>
+        <v>0.2828</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3398</v>
+        <v>-0.2639</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.6483</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5214</v>
+        <v>1.3265</v>
       </c>
       <c r="F17" t="n">
         <v>-0.6783</v>
@@ -1780,10 +1780,10 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4609</v>
+        <v>0.266</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4267</v>
+        <v>0.2319</v>
       </c>
       <c r="U17" t="n">
         <v>0.0341</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>J. MARTINEZ MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1102</v>
+        <v>0.6032</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2572</v>
+        <v>0.3786</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3675</v>
+        <v>0.2247</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2406</v>
+        <v>-0.5582</v>
       </c>
       <c r="H18" t="n">
-        <v>0.853</v>
+        <v>-1.8939</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.3357</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3271</v>
+        <v>0.9759</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8533</v>
+        <v>-0.3162</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5262</v>
+        <v>1.2921</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0865</v>
+        <v>-1.534</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0003</v>
+        <v>-1.5777</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0863</v>
+        <v>0.0437</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3698</v>
+        <v>-1.2351</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1945</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5643</v>
+        <v>-0.6378</v>
       </c>
       <c r="V18" t="n">
-        <v>0.019</v>
+        <v>0.3208</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6036</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUNOZ</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1833</v>
+        <v>-0.4651</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0112</v>
+        <v>0.7701</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1721</v>
+        <v>-1.2352</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5582</v>
+        <v>0.2406</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8939</v>
+        <v>0.853</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3357</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9759</v>
+        <v>2.3271</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3162</v>
+        <v>2.8533</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2921</v>
+        <v>-0.5262</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.534</v>
+        <v>-2.0865</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5777</v>
+        <v>-2.0003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0437</v>
+        <v>-0.0863</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0216</v>
+        <v>-0.7247</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9871</v>
+        <v>-0.2927</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0346</v>
+        <v>-0.432</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3208</v>
+        <v>0.019</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3208</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6601</v>
+        <v>-0.5723</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7391</v>
+        <v>-1.8365</v>
       </c>
       <c r="F20" t="n">
-        <v>1.079</v>
+        <v>1.2642</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6385</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0406</v>
+        <v>0.0472</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0617</v>
+        <v>-0.0357</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1023</v>
+        <v>0.0829</v>
       </c>
       <c r="V20" t="n">
         <v>0.6415999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7427</v>
+        <v>-1.3349</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2494</v>
+        <v>-1.7622</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5067</v>
+        <v>0.4273</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7514</v>
@@ -2170,13 +2170,13 @@
         <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7271</v>
+        <v>-0.3193</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7055</v>
+        <v>-0.2183</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0217</v>
+        <v>-0.1011</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6415999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0341</v>
+        <v>-1.7074</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1989</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-2.3378</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1163</v>
+        <v>0.133</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2678</v>
+        <v>0.7239</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1515</v>
+        <v>-0.5909</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0408</v>
+        <v>1.6612</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0408</v>
+        <v>2.1873</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0755</v>
+        <v>-1.5281</v>
       </c>
       <c r="N23" t="n">
-        <v>0.227</v>
+        <v>-1.4634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1515</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2069</v>
+        <v>-0.0858</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3527</v>
+        <v>-0.0682</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1458</v>
+        <v>-0.0176</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2452</v>
+        <v>-2.5094</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1236</v>
+        <v>-1.7599</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2407</v>
+        <v>-1.004</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3643</v>
+        <v>-0.7558</v>
       </c>
       <c r="G24" t="n">
-        <v>0.133</v>
+        <v>1.1163</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7239</v>
+        <v>1.2678</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5909</v>
+        <v>-0.1515</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6612</v>
+        <v>1.0408</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1873</v>
+        <v>1.0408</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5281</v>
+        <v>0.0755</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4634</v>
+        <v>0.227</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1515</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7548</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.502</v>
+        <v>0.0673</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.458</v>
+        <v>-0.1579</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.044</v>
+        <v>0.2252</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5094</v>
+        <v>-1.2452</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8904</v>
+        <v>-2.793</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7008</v>
+        <v>-1.6034</v>
       </c>
       <c r="F25" t="n">
         <v>-1.1896</v>
@@ -2404,10 +2404,10 @@
         <v>0.3774</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6031</v>
+        <v>-0.5057</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1147</v>
+        <v>-0.0172</v>
       </c>
       <c r="U25" t="n">
         <v>-0.4884</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4361</v>
+        <v>-6.4362</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.2852</v>
+        <v>-2.2849</v>
       </c>
       <c r="F26" t="n">
         <v>-4.1511</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.129799999999999</v>
+        <v>-1.1298</v>
       </c>
       <c r="H26" t="n">
         <v>3.0911</v>
@@ -2467,10 +2467,10 @@
         <v>-8.2143</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.567499999999999</v>
+        <v>-7.567500000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6468999999999999</v>
+        <v>-0.6469</v>
       </c>
       <c r="P26" t="n">
         <v>1.887</v>
@@ -2482,13 +2482,13 @@
         <v>11.322</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.8355</v>
+        <v>-3.8357</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0288</v>
+        <v>-2.0285</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8071</v>
+        <v>-1.8072</v>
       </c>
       <c r="V26" t="n">
         <v>-3.3578</v>
